--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -511,7 +511,7 @@
         <v>46169</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>46170.51050925926</v>
+        <v>46170.52391203704</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,35 @@
         <v>46170.52391203704</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>46171.71282059028</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>46171.74888888889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -540,7 +540,7 @@
         <v>46171</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>46171.74888888889</v>
+        <v>46172.46278935186</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -543,6 +543,35 @@
         <v>46172.46278935186</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>46172.91682571759</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>46173.49479166666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,35 @@
         <v>46173.49479166666</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>46174.74406888889</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>46174.87868055556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -598,7 +598,7 @@
         <v>46174</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>46174.87868055556</v>
+        <v>46175.45627314815</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -601,6 +601,35 @@
         <v>46175.45627314815</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>46175.71332149306</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>46175</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>46175.79332175926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -627,7 +627,7 @@
         <v>46175</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>46175.79332175926</v>
+        <v>46176.31851851852</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -630,6 +630,35 @@
         <v>46176.31851851852</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>46176.71280685185</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>46176.83378472222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -659,6 +659,35 @@
         <v>46176.83378472222</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>46177.72341887731</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>46177</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>46177.73148148148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -685,7 +685,7 @@
         <v>46177</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>46177.73148148148</v>
+        <v>46178.67767361111</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -688,6 +688,35 @@
         <v>46178.67767361111</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>46178.74416739583</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>46179.46702546296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -717,6 +717,35 @@
         <v>46179.46702546296</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>46179.91685921296</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>46179</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>46180.50589120371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -746,6 +746,35 @@
         <v>46180.50589120371</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>46181.723221875</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>46181.7343287037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -772,7 +772,7 @@
         <v>46181</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>46181.7343287037</v>
+        <v>46182.68061342592</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -775,6 +775,35 @@
         <v>46182.68061342592</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>46183.71281974537</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>46183</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>46183.73940972222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -804,6 +804,35 @@
         <v>46183.73940972222</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>46184.71297414352</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>46184.74891203704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -830,7 +830,7 @@
         <v>46184</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>46184.74891203704</v>
+        <v>46185.69061342593</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -833,6 +833,35 @@
         <v>46185.69061342593</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>46185.72327106482</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>46186.50675925926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -862,6 +862,35 @@
         <v>46186.50675925926</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>46186.91684469907</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>46186</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>46187.52033564815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -891,6 +891,35 @@
         <v>46187.52033564815</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>46203.70235994213</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>46204.41221064814</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -920,6 +920,35 @@
         <v>46204.41221064814</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>46204.71334084491</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>46205.386875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -949,6 +949,35 @@
         <v>46205.386875</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>46205.71304541667</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>46205</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>46206.39075231482</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -978,6 +978,35 @@
         <v>46206.39075231482</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>46206.91684921296</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>46207.36202546296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1007,35 @@
         <v>46207.36202546296</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>46207.9170674074</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>46207</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>46208.37265046296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1036,6 +1036,35 @@
         <v>46208.37265046296</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>46208.91707025463</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>46208</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>46209.44590277778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1065,35 @@
         <v>46209.44590277778</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>46209.72347792824</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>46210.40766203704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1094,6 +1094,35 @@
         <v>46210.40766203704</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>46210.71328763889</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>46210</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>46211.35662037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1123,6 +1123,35 @@
         <v>46211.35662037037</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>46212.77590881944</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>46212</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>46213.40269675926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1152,6 +1152,35 @@
         <v>46213.40269675926</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>46213.72378505787</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>46213</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>46214.33349537037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,35 @@
         <v>46214.33349537037</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>46214.91715153935</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>46214</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>46215.3483449074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1210,6 +1210,35 @@
         <v>46215.3483449074</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>46215.91696012732</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>46216.3975</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1239,6 +1239,35 @@
         <v>46216.3975</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>46216.7122725463</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>46216</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>46217.34075231481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,35 @@
         <v>46217.34075231481</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>46217.72269025463</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>46218.34554398148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1297,35 @@
         <v>46218.34554398148</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>46219.00076973379</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>46219.34598379629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1326,6 +1326,35 @@
         <v>46219.34598379629</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>46220.00075875</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>46220.34263888889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1355,6 +1355,35 @@
         <v>46220.34263888889</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>46221.00121206018</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>46221.33006944445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1381,7 +1381,7 @@
         <v>46221</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>46221.33006944445</v>
+        <v>46222.34947916667</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1381,7 +1381,7 @@
         <v>46221</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>46222.34947916667</v>
+        <v>46223.38835648148</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1384,6 +1384,35 @@
         <v>46223.38835648148</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>46223.72310943287</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>46224.35626157407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1413,6 +1413,35 @@
         <v>46224.35626157407</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>46224.76459033565</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>46225.35607638889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1442,6 +1442,35 @@
         <v>46225.35607638889</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>46225.75104449074</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>46225</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>46226.35717592593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1471,6 +1471,35 @@
         <v>46226.35717592593</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>46226.74386270833</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>46226</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>46227.35533564815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1500,6 +1500,35 @@
         <v>46227.35533564815</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>46227.77170729166</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>46228.33989583333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1526,7 +1526,7 @@
         <v>46227</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>46228.33989583333</v>
+        <v>46229.35425925926</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1526,7 +1526,7 @@
         <v>46227</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>46229.35425925926</v>
+        <v>46230.41413194445</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1529,6 +1529,35 @@
         <v>46230.41413194445</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>46230.72323027778</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>46231.35966435185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1558,6 +1558,35 @@
         <v>46231.35966435185</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>46231.72315858796</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>46231</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>46232.36434027777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1587,6 +1587,35 @@
         <v>46232.36434027777</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>46232.71252984954</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>46233.35444444444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1616,6 +1616,35 @@
         <v>46233.35444444444</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46234.71257607639</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>46235.35011574074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1642,7 +1642,7 @@
         <v>46234</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>46235.35011574074</v>
+        <v>46236.35216435185</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1642,7 +1642,7 @@
         <v>46234</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>46236.35216435185</v>
+        <v>46237.4100925926</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1645,6 +1645,35 @@
         <v>46237.4100925926</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>46237.71277626157</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>46238.36158564815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1674,6 +1674,35 @@
         <v>46238.36158564815</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>46238.73326049768</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>46239.36069444445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1703,6 +1703,35 @@
         <v>46239.36069444445</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>46239.71966368055</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>46240.36125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1732,6 +1732,35 @@
         <v>46240.36125</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>46240.71948996527</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>46241.30519675926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,35 @@
         <v>46241.30519675926</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>46241.72314488426</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>46242.28939814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1787,7 +1787,7 @@
         <v>46241</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>46242.28939814815</v>
+        <v>46243.29163194444</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1787,7 +1787,7 @@
         <v>46241</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>46243.29163194444</v>
+        <v>46244.32333333333</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1790,6 +1790,35 @@
         <v>46244.32333333333</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>46244.77504319444</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>46245.29967592593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1819,6 +1819,35 @@
         <v>46245.29967592593</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>46245.71251248843</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>46246.31078703704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1848,6 +1848,35 @@
         <v>46246.31078703704</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>46246.73343768519</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>46247.31787037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1877,6 +1877,35 @@
         <v>46247.31787037037</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>46247.71976072917</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>46248.31057870371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1906,6 +1906,35 @@
         <v>46248.31057870371</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>46249.01107883102</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>46249</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>46249.27850694444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1935,6 +1935,35 @@
         <v>46249.27850694444</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>46250.00109225694</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>46250.27930555555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -1961,7 +1961,7 @@
         <v>46250</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>46250.27930555555</v>
+        <v>46251.29128472223</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1964,6 +1964,35 @@
         <v>46251.29128472223</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>46251.75414839121</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>46252.28260416666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1993,6 +1993,35 @@
         <v>46252.28260416666</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>46252.76115584491</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>46252</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>46253.28326388889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2022,6 +2022,35 @@
         <v>46253.28326388889</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>46253.7542890162</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>46254.28486111111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2051,6 +2051,35 @@
         <v>46254.28486111111</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>46254.73370774306</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>46255.28542824074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2080,35 @@
         <v>46255.28542824074</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>46255.7542290625</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>46256.27953703704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2106,7 +2106,7 @@
         <v>46255</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>46256.27953703704</v>
+        <v>46257.28064814815</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2106,7 +2106,7 @@
         <v>46255</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>46257.28064814815</v>
+        <v>46258.29322916667</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2109,6 +2109,35 @@
         <v>46258.29322916667</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>46258.72303645833</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>46259.28627314815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2138,6 +2138,35 @@
         <v>46259.28627314815</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>46259.72294965278</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>46260.28708333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2167,35 @@
         <v>46260.28708333334</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>46260.75445328704</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>46261.72686342592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2196,6 +2196,35 @@
         <v>46261.72686342592</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>46262.75432079861</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>46262.76391203704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2222,7 +2222,7 @@
         <v>46262</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>46262.76391203704</v>
+        <v>46263.51986111111</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2222,7 +2222,7 @@
         <v>46262</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>46263.51986111111</v>
+        <v>46264.47917824074</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2222,7 +2222,7 @@
         <v>46262</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>46264.47917824074</v>
+        <v>46265.54328703704</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2225,35 @@
         <v>46265.54328703704</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>46265.77516318287</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>46266.47131944444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2254,6 +2254,35 @@
         <v>46266.47131944444</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>46266.76120681713</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>46267.45337962963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2283,6 +2283,35 @@
         <v>46267.45337962963</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>46267.76494193287</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>46267</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>46268.45314814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2309,7 +2309,7 @@
         <v>46267</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>46268.45314814815</v>
+        <v>46269.45266203704</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2312,6 +2312,35 @@
         <v>46269.45266203704</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>46270.01817428241</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>46270.4240625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2338,7 +2338,7 @@
         <v>46270</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>46270.4240625</v>
+        <v>46271.43844907408</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2338,7 +2338,7 @@
         <v>46270</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>46271.43844907408</v>
+        <v>46272.49618055556</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -2338,7 +2338,7 @@
         <v>46270</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>46272.49618055556</v>
+        <v>46273.45206018518</v>
       </c>
     </row>
   </sheetData>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2341,6 +2341,35 @@
         <v>46273.45206018518</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>46274.00112909723</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>46274.4560300926</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2370,6 +2370,35 @@
         <v>46274.4560300926</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>46275.00086740741</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>46275</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>46275.45361111111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2399,6 +2399,35 @@
         <v>46275.45361111111</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>46276.00439994213</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>46276.45148148148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_JKM_Price.xlsx
+++ b/Historico_JKM_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2428,35 @@
         <v>46276.45148148148</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>46277.00078336806</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>46277</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>46277.42944444445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
